--- a/AAPL_Financial_Model.xlsx
+++ b/AAPL_Financial_Model.xlsx
@@ -24,13 +24,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="0.0000%"/>
+    <numFmt numFmtId="170" formatCode="0.00000000"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -142,6 +145,12 @@
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -203,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -303,25 +312,34 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -334,6 +352,30 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -351,19 +393,13 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3217,7 +3253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3479,416 +3515,382 @@
         <v>0.025</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Exit Multiple (EV/EBITDA ×)</t>
+        </is>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  STEP 1: PROJECT UNLEVERED FREE CASH FLOWS</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="17" t="n"/>
-      <c r="G14" s="17" t="n"/>
-      <c r="H14" s="17" t="n"/>
-      <c r="I14" s="17" t="n"/>
-      <c r="J14" s="17" t="n"/>
-      <c r="K14" s="17" t="n"/>
-      <c r="L14" s="17" t="n"/>
-      <c r="M14" s="17" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Revenue ($M)</t>
-        </is>
-      </c>
-      <c r="B15" s="41" t="n">
-        <v>451442.016256</v>
-      </c>
-      <c r="C15" s="26">
-        <f>B15*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="26">
-        <f>C15*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="26">
-        <f>D15*(1+E5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="26">
-        <f>E15*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="26">
-        <f>F15*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>Base = last reported revenue; forecast years grow at assumed rate above</t>
-        </is>
-      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="17" t="n"/>
+      <c r="M15" s="17" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>EBIT ($M)</t>
-        </is>
-      </c>
-      <c r="B16" s="26">
-        <f>B15*B6</f>
-        <v/>
+          <t>Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B16" s="42" t="n">
+        <v>451442.016256</v>
       </c>
       <c r="C16" s="26">
-        <f>C15*C6</f>
+        <f>B16*(1+C5)</f>
         <v/>
       </c>
       <c r="D16" s="26">
-        <f>D15*D6</f>
+        <f>C16*(1+D5)</f>
         <v/>
       </c>
       <c r="E16" s="26">
-        <f>E15*E6</f>
+        <f>D16*(1+E5)</f>
         <v/>
       </c>
       <c r="F16" s="26">
-        <f>F15*F6</f>
+        <f>E16*(1+F5)</f>
         <v/>
       </c>
       <c r="G16" s="26">
-        <f>G15*G6</f>
-        <v/>
-      </c>
-      <c r="I16" s="22">
-        <f> Revenue × EBIT Margin; operating profit before interest &amp; tax</f>
-        <v/>
+        <f>F16*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>Base = last reported revenue; forecast years grow at assumed rate above</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
+          <t>EBIT ($M)</t>
+        </is>
+      </c>
+      <c r="B17" s="26">
+        <f>B16*B6</f>
+        <v/>
+      </c>
+      <c r="C17" s="26">
+        <f>C16*C6</f>
+        <v/>
+      </c>
+      <c r="D17" s="26">
+        <f>D16*D6</f>
+        <v/>
+      </c>
+      <c r="E17" s="26">
+        <f>E16*E6</f>
+        <v/>
+      </c>
+      <c r="F17" s="26">
+        <f>F16*F6</f>
+        <v/>
+      </c>
+      <c r="G17" s="26">
+        <f>G16*G6</f>
+        <v/>
+      </c>
+      <c r="I17" s="22">
+        <f> Revenue × EBIT Margin; operating profit before interest &amp; tax</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
           <t>NOPAT = EBIT × (1 – Tax Rate)</t>
         </is>
       </c>
-      <c r="B17" s="26">
-        <f>B16*(1-B7)</f>
-        <v/>
-      </c>
-      <c r="C17" s="26">
-        <f>C16*(1-C7)</f>
-        <v/>
-      </c>
-      <c r="D17" s="26">
-        <f>D16*(1-D7)</f>
-        <v/>
-      </c>
-      <c r="E17" s="26">
-        <f>E16*(1-E7)</f>
-        <v/>
-      </c>
-      <c r="F17" s="26">
-        <f>F16*(1-F7)</f>
-        <v/>
-      </c>
-      <c r="G17" s="26">
-        <f>G16*(1-G7)</f>
-        <v/>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="B18" s="26">
+        <f>B17*(1-B7)</f>
+        <v/>
+      </c>
+      <c r="C18" s="26">
+        <f>C17*(1-C7)</f>
+        <v/>
+      </c>
+      <c r="D18" s="26">
+        <f>D17*(1-D7)</f>
+        <v/>
+      </c>
+      <c r="E18" s="26">
+        <f>E17*(1-E7)</f>
+        <v/>
+      </c>
+      <c r="F18" s="26">
+        <f>F17*(1-F7)</f>
+        <v/>
+      </c>
+      <c r="G18" s="26">
+        <f>G17*(1-G7)</f>
+        <v/>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Net Operating Profit After Tax; removes financing effects for unlevered view</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
-        <is>
-          <t>Add: D&amp;A ($M)</t>
-        </is>
-      </c>
-      <c r="B18" s="26">
-        <f>B15*B8</f>
-        <v/>
-      </c>
-      <c r="C18" s="26">
-        <f>C15*C8</f>
-        <v/>
-      </c>
-      <c r="D18" s="26">
-        <f>D15*D8</f>
-        <v/>
-      </c>
-      <c r="E18" s="26">
-        <f>E15*E8</f>
-        <v/>
-      </c>
-      <c r="F18" s="26">
-        <f>F15*F8</f>
-        <v/>
-      </c>
-      <c r="G18" s="26">
-        <f>G15*G8</f>
-        <v/>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>Non-cash charge added back; reduces IS earnings but not a cash outflow</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="32" t="inlineStr">
         <is>
-          <t>Less: CapEx ($M)</t>
+          <t>Add: D&amp;A ($M)</t>
         </is>
       </c>
       <c r="B19" s="26">
-        <f>-B15*B9</f>
+        <f>B16*B8</f>
         <v/>
       </c>
       <c r="C19" s="26">
-        <f>-C15*C9</f>
+        <f>C16*C8</f>
         <v/>
       </c>
       <c r="D19" s="26">
-        <f>-D15*D9</f>
+        <f>D16*D8</f>
         <v/>
       </c>
       <c r="E19" s="26">
-        <f>-E15*E9</f>
+        <f>E16*E8</f>
         <v/>
       </c>
       <c r="F19" s="26">
-        <f>-F15*F9</f>
+        <f>F16*F8</f>
         <v/>
       </c>
       <c r="G19" s="26">
-        <f>-G15*G9</f>
+        <f>G16*G8</f>
         <v/>
       </c>
       <c r="I19" s="22" t="inlineStr">
         <is>
-          <t>Capital expenditure; shown negative (cash outflow to build/maintain assets)</t>
+          <t>Non-cash charge added back; reduces IS earnings but not a cash outflow</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="32" t="inlineStr">
         <is>
+          <t>Less: CapEx ($M)</t>
+        </is>
+      </c>
+      <c r="B20" s="26">
+        <f>-B16*B9</f>
+        <v/>
+      </c>
+      <c r="C20" s="26">
+        <f>-C16*C9</f>
+        <v/>
+      </c>
+      <c r="D20" s="26">
+        <f>-D16*D9</f>
+        <v/>
+      </c>
+      <c r="E20" s="26">
+        <f>-E16*E9</f>
+        <v/>
+      </c>
+      <c r="F20" s="26">
+        <f>-F16*F9</f>
+        <v/>
+      </c>
+      <c r="G20" s="26">
+        <f>-G16*G9</f>
+        <v/>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
+        <is>
+          <t>Capital expenditure; shown negative (cash outflow to build/maintain assets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
           <t>Less: Change in NWC ($M)</t>
         </is>
       </c>
-      <c r="C20" s="26">
-        <f>-(C15-B15)*C10</f>
-        <v/>
-      </c>
-      <c r="D20" s="26">
-        <f>-(D15-C15)*D10</f>
-        <v/>
-      </c>
-      <c r="E20" s="26">
-        <f>-(E15-D15)*E10</f>
-        <v/>
-      </c>
-      <c r="F20" s="26">
-        <f>-(F15-E15)*F10</f>
-        <v/>
-      </c>
-      <c r="G20" s="26">
-        <f>-(G15-F15)*G10</f>
-        <v/>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="C21" s="26">
+        <f>-(C16-B16)*C10</f>
+        <v/>
+      </c>
+      <c r="D21" s="26">
+        <f>-(D16-C16)*D10</f>
+        <v/>
+      </c>
+      <c r="E21" s="26">
+        <f>-(E16-D16)*E10</f>
+        <v/>
+      </c>
+      <c r="F21" s="26">
+        <f>-(F16-E16)*F10</f>
+        <v/>
+      </c>
+      <c r="G21" s="26">
+        <f>-(G16-F16)*G10</f>
+        <v/>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>Incremental working capital needed as business grows; negative = cash used</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>UNLEVERED FREE CASH FLOW</t>
         </is>
       </c>
-      <c r="C21" s="19">
-        <f>C17+C18+C19+C20</f>
-        <v/>
-      </c>
-      <c r="D21" s="19">
-        <f>D17+D18+D19+D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="19">
-        <f>E17+E18+E19+E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="19">
-        <f>F17+F18+F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="19">
-        <f>G17+G18+G19+G20</f>
-        <v/>
-      </c>
-      <c r="I21" s="22">
+      <c r="C22" s="19">
+        <f>C18+C19+C20+C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="19">
+        <f>D18+D19+D20+D21</f>
+        <v/>
+      </c>
+      <c r="E22" s="19">
+        <f>E18+E19+E20+E21</f>
+        <v/>
+      </c>
+      <c r="F22" s="19">
+        <f>F18+F19+F20+F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="19">
+        <f>G18+G19+G20+G21</f>
+        <v/>
+      </c>
+      <c r="I22" s="22">
         <f> NOPAT + D&amp;A − CapEx − ΔNWC; pre-financing cash available to all capital providers</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  STEP 2: TERMINAL VALUE (Gordon Growth Model)</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="17" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="17" t="n"/>
-      <c r="L23" s="17" t="n"/>
-      <c r="M23" s="17" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="17" t="n"/>
+      <c r="L24" s="17" t="n"/>
+      <c r="M24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>TV = Final UFCF × (1+g) / (WACC – g)</t>
         </is>
       </c>
-      <c r="B24" s="19">
-        <f>G21*(1+B12)/(B11-B12)</f>
-        <v/>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="B25" s="19">
+        <f>G22*(1+B12)/(B11-B12)</f>
+        <v/>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>Gordon Growth Model; WACC must exceed g or result is undefined — adjust assumptions if negative</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STEP 3: DISCOUNT TO PRESENT VALUE</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="17" t="n"/>
-      <c r="H26" s="17" t="n"/>
-      <c r="I26" s="17" t="n"/>
-      <c r="J26" s="17" t="n"/>
-      <c r="K26" s="17" t="n"/>
-      <c r="L26" s="17" t="n"/>
-      <c r="M26" s="17" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>Year Number</t>
-        </is>
-      </c>
-      <c r="C27" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="F27" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="G27" s="42" t="n">
-        <v>5</v>
-      </c>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 2B: TERMINAL VALUE (Exit Multiple Method — EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
+      <c r="K27" s="17" t="n"/>
+      <c r="L27" s="17" t="n"/>
+      <c r="M27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>PV Discount Factor = 1 / (1+WACC)^n</t>
-        </is>
-      </c>
-      <c r="C28" s="43">
-        <f>1/(1+$B$11)^C27</f>
-        <v/>
-      </c>
-      <c r="D28" s="43">
-        <f>1/(1+$B$11)^D27</f>
-        <v/>
-      </c>
-      <c r="E28" s="43">
-        <f>1/(1+$B$11)^E27</f>
-        <v/>
-      </c>
-      <c r="F28" s="43">
-        <f>1/(1+$B$11)^F27</f>
-        <v/>
-      </c>
-      <c r="G28" s="43">
-        <f>1/(1+$B$11)^G27</f>
-        <v/>
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>Year 5 EBITDA = EBIT + D&amp;A</t>
+        </is>
+      </c>
+      <c r="B28" s="21">
+        <f>G17+G19</f>
+        <v/>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>Year 5 projected EBIT + D&amp;A from assumptions above; exit multiple applied to this</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
-        <is>
-          <t>PV of Each UFCF</t>
-        </is>
-      </c>
-      <c r="C29" s="21">
-        <f>C21*C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="21">
-        <f>D21*D28</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>E21*E28</f>
-        <v/>
-      </c>
-      <c r="F29" s="21">
-        <f>F21*F28</f>
-        <v/>
-      </c>
-      <c r="G29" s="21">
-        <f>G21*G28</f>
-        <v/>
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="B29" s="43">
+        <f>H13</f>
+        <v/>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>From assumption table above (col H); update based on peer median in Trading Comps</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>PV of Terminal Value</t>
+          <t>TV = Year 5 EBITDA × Exit Multiple</t>
         </is>
       </c>
       <c r="B30" s="19">
-        <f>B24/(1+$B$11)^5</f>
+        <f>B28*B29</f>
         <v/>
       </c>
       <c r="I30" s="22" t="inlineStr">
         <is>
-          <t>Terminal Value discounted back 5 years at WACC; typically 60-80% of total EV</t>
+          <t>EV at Year 5 using market-based multiple; alternative to perpetuity growth (GGM)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STEP 4: BRIDGE TO EQUITY VALUE PER SHARE</t>
+          <t xml:space="preserve">  STEP 3: DISCOUNT TO PRESENT VALUE</t>
         </is>
       </c>
       <c r="B32" s="17" t="n"/>
@@ -3907,290 +3909,707 @@
     <row r="33">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>Sum of PV of UFCFs (Years 1–5)</t>
-        </is>
-      </c>
-      <c r="B33" s="26">
-        <f>SUM(C29:G29)</f>
-        <v/>
+          <t>Year Number</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="32" t="inlineStr">
         <is>
+          <t>PV Discount Factor = 1 / (1+WACC)^n</t>
+        </is>
+      </c>
+      <c r="C34" s="45">
+        <f>1/(1+$B$11)^C33</f>
+        <v/>
+      </c>
+      <c r="D34" s="45">
+        <f>1/(1+$B$11)^D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="45">
+        <f>1/(1+$B$11)^E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="45">
+        <f>1/(1+$B$11)^F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="45">
+        <f>1/(1+$B$11)^G33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>PV of Each UFCF</t>
+        </is>
+      </c>
+      <c r="C35" s="21">
+        <f>C22*C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="21">
+        <f>D22*D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="21">
+        <f>E22*E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="21">
+        <f>F22*F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="21">
+        <f>G22*G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t>PV of Terminal Value (GGM)</t>
+        </is>
+      </c>
+      <c r="B36" s="19">
+        <f>B25/(1+$B$11)^5</f>
+        <v/>
+      </c>
+      <c r="I36" s="22" t="inlineStr">
+        <is>
+          <t>GGM Terminal Value discounted back 5 years at WACC; typically 60-80% of total EV</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t>PV of Terminal Value (Exit Multiple)</t>
+        </is>
+      </c>
+      <c r="B37" s="19">
+        <f>B30/(1+$B$11)^5</f>
+        <v/>
+      </c>
+      <c r="I37" s="22" t="inlineStr">
+        <is>
+          <t>Exit Multiple TV discounted back 5 years at WACC</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 4: BRIDGE TO EQUITY VALUE PER SHARE</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="17" t="n"/>
+      <c r="H39" s="17" t="n"/>
+      <c r="I39" s="17" t="n"/>
+      <c r="J39" s="17" t="n"/>
+      <c r="K39" s="17" t="n"/>
+      <c r="L39" s="17" t="n"/>
+      <c r="M39" s="17" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Sum of PV of UFCFs (Years 1–5)</t>
+        </is>
+      </c>
+      <c r="B40" s="26">
+        <f>SUM(C35:G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
           <t>PV of Terminal Value</t>
         </is>
       </c>
-      <c r="B34" s="33">
-        <f>B30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="B41" s="33">
+        <f>B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>TV as % of Total EV</t>
         </is>
       </c>
-      <c r="B35" s="25">
-        <f>B34/(B33+B34)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="B42" s="25">
+        <f>B41/(B40+B41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>ENTERPRISE VALUE (DCF)</t>
         </is>
       </c>
-      <c r="B36" s="19">
-        <f>B33+B34</f>
-        <v/>
-      </c>
-      <c r="I36" s="22">
+      <c r="B43" s="19">
+        <f>B40+B41</f>
+        <v/>
+      </c>
+      <c r="I43" s="22">
         <f> PV of FCFs + PV of Terminal Value; value of the whole enterprise (debt + equity)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>Add: Cash &amp; Equivalents ($M)</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n">
+      <c r="B44" s="26" t="n">
         <v>68507.00083200001</v>
       </c>
-      <c r="I37" s="22" t="inlineStr">
+      <c r="I44" s="22" t="inlineStr">
         <is>
           <t>Cash is non-operating; added back to convert EV → Equity Value</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="23" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>Less: Total Debt ($M)</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n">
+      <c r="B45" s="26" t="n">
         <v>-84710.998016</v>
       </c>
-      <c r="I38" s="22" t="inlineStr">
+      <c r="I45" s="22" t="inlineStr">
         <is>
           <t>Debt holders have prior claim; deducted to get equity holders' value</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="27" t="inlineStr">
-        <is>
-          <t>Equity Value ($M)</t>
-        </is>
-      </c>
-      <c r="B39" s="28">
-        <f>B36+B37+B38</f>
-        <v/>
-      </c>
-      <c r="I39" s="22">
-        <f> Enterprise Value + Cash − Debt; total value attributable to equity holders</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="23" t="inlineStr">
-        <is>
-          <t>Diluted Shares Outstanding (M)</t>
-        </is>
-      </c>
-      <c r="B40" s="34" t="n">
-        <v>14687.356</v>
-      </c>
-      <c r="I40" s="22" t="inlineStr">
-        <is>
-          <t>Diluted count includes options and RSUs; source: Yahoo Finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="inlineStr">
-        <is>
-          <t>INTRINSIC VALUE PER SHARE (DCF)</t>
-        </is>
-      </c>
-      <c r="B41" s="44">
-        <f>B39/B40</f>
-        <v/>
-      </c>
-      <c r="I41" s="22">
-        <f> Equity Value / Diluted Shares; compare to current market price for buy/sell signal</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STEP 5: SENSITIVITY — Share Price vs WACC &amp; Terminal Growth Rate</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="17" t="n"/>
-      <c r="H43" s="17" t="n"/>
-      <c r="I43" s="17" t="n"/>
-      <c r="J43" s="17" t="n"/>
-      <c r="K43" s="17" t="n"/>
-      <c r="L43" s="17" t="n"/>
-      <c r="M43" s="17" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="inlineStr">
-        <is>
-          <t>→ Terminal Growth Rate (g)</t>
-        </is>
-      </c>
-      <c r="C44" s="45" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D44" s="45" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E44" s="45" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="F44" s="45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G44" s="45" t="n">
-        <v>0.035</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>WACC = 9.6%</t>
-        </is>
-      </c>
-      <c r="B45" s="25" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="C45" s="46" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="D45" s="46" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="E45" s="46" t="n">
-        <v>71.54000000000001</v>
-      </c>
-      <c r="F45" s="46" t="n">
-        <v>77.34</v>
-      </c>
-      <c r="G45" s="46" t="n">
-        <v>84.08</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="27" t="inlineStr">
         <is>
+          <t>Equity Value ($M)</t>
+        </is>
+      </c>
+      <c r="B46" s="28">
+        <f>B43+B44+B45</f>
+        <v/>
+      </c>
+      <c r="I46" s="22">
+        <f> Enterprise Value + Cash − Debt; total value attributable to equity holders</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Diluted Shares Outstanding (M)</t>
+        </is>
+      </c>
+      <c r="B47" s="34" t="n">
+        <v>14687.356</v>
+      </c>
+      <c r="I47" s="22" t="inlineStr">
+        <is>
+          <t>Diluted count includes options and RSUs; source: Yahoo Finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>INTRINSIC VALUE PER SHARE (GGM)</t>
+        </is>
+      </c>
+      <c r="B48" s="46">
+        <f>B46/B47</f>
+        <v/>
+      </c>
+      <c r="I48" s="22">
+        <f> Equity Value / Diluted Shares; compare to current market price for buy/sell signal</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 4B: BRIDGE TO EQUITY VALUE — EXIT MULTIPLE METHOD</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="17" t="n"/>
+      <c r="H50" s="17" t="n"/>
+      <c r="I50" s="17" t="n"/>
+      <c r="J50" s="17" t="n"/>
+      <c r="K50" s="17" t="n"/>
+      <c r="L50" s="17" t="n"/>
+      <c r="M50" s="17" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>Sum of PV of UFCFs (Years 1–5)</t>
+        </is>
+      </c>
+      <c r="B51" s="26">
+        <f>SUM(C35:G35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>PV of Terminal Value (Exit Multiple)</t>
+        </is>
+      </c>
+      <c r="B52" s="33">
+        <f>B37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="29" t="inlineStr">
+        <is>
+          <t>TV as % of Total EV (Exit Method)</t>
+        </is>
+      </c>
+      <c r="B53" s="25">
+        <f>B52/(B51+B52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>ENTERPRISE VALUE (Exit Multiple Method)</t>
+        </is>
+      </c>
+      <c r="B54" s="19">
+        <f>B51+B52</f>
+        <v/>
+      </c>
+      <c r="I54" s="22">
+        <f> PV UFCFs + PV Exit TV; parallel to GGM EV above</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>Add: Cash &amp; Equivalents ($M)</t>
+        </is>
+      </c>
+      <c r="B55" s="26" t="n">
+        <v>68507.00083200001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>Less: Total Debt ($M)</t>
+        </is>
+      </c>
+      <c r="B56" s="26" t="n">
+        <v>-84710.998016</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="27" t="inlineStr">
+        <is>
+          <t>Equity Value — Exit Multiple ($M)</t>
+        </is>
+      </c>
+      <c r="B57" s="28">
+        <f>B54+B55+B56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>Diluted Shares Outstanding (M)</t>
+        </is>
+      </c>
+      <c r="B58" s="34" t="n">
+        <v>14687.356</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>INTRINSIC VALUE PER SHARE (Exit Multiple)</t>
+        </is>
+      </c>
+      <c r="B59" s="46">
+        <f>B57/B58</f>
+        <v/>
+      </c>
+      <c r="I59" s="22" t="inlineStr">
+        <is>
+          <t>Parallel to GGM method; uses market-based exit multiple instead of perpetuity growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 5: SENSITIVITY — Share Price vs WACC &amp; Terminal Growth Rate</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="F61" s="17" t="n"/>
+      <c r="G61" s="17" t="n"/>
+      <c r="H61" s="17" t="n"/>
+      <c r="I61" s="17" t="n"/>
+      <c r="J61" s="17" t="n"/>
+      <c r="K61" s="17" t="n"/>
+      <c r="L61" s="17" t="n"/>
+      <c r="M61" s="17" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="29" t="inlineStr">
+        <is>
+          <t>→ Terminal Growth Rate (g)</t>
+        </is>
+      </c>
+      <c r="C62" s="47" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D62" s="47" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E62" s="47" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F62" s="47" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G62" s="47" t="n">
+        <v>0.035</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>WACC = 9.6%</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C63" s="48" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="D63" s="48" t="n">
+        <v>66.51000000000001</v>
+      </c>
+      <c r="E63" s="48" t="n">
+        <v>71.54000000000001</v>
+      </c>
+      <c r="F63" s="48" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="G63" s="48" t="n">
+        <v>84.08</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="27" t="inlineStr">
+        <is>
           <t>WACC = 10.6%</t>
         </is>
       </c>
-      <c r="B46" s="25" t="n">
+      <c r="B64" s="25" t="n">
         <v>0.106</v>
       </c>
-      <c r="C46" s="46" t="n">
+      <c r="C64" s="48" t="n">
         <v>52.82</v>
       </c>
-      <c r="D46" s="46" t="n">
+      <c r="D64" s="48" t="n">
         <v>56.17</v>
       </c>
-      <c r="E46" s="46" t="n">
+      <c r="E64" s="48" t="n">
         <v>59.93</v>
       </c>
-      <c r="F46" s="46" t="n">
+      <c r="F64" s="48" t="n">
         <v>64.18000000000001</v>
       </c>
-      <c r="G46" s="46" t="n">
+      <c r="G64" s="48" t="n">
         <v>69.03</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="27" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t>WACC = 11.6%</t>
         </is>
       </c>
-      <c r="B47" s="25" t="n">
+      <c r="B65" s="25" t="n">
         <v>0.116</v>
       </c>
-      <c r="C47" s="46" t="n">
+      <c r="C65" s="48" t="n">
         <v>45.5</v>
       </c>
-      <c r="D47" s="46" t="n">
+      <c r="D65" s="48" t="n">
         <v>48.1</v>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E65" s="49" t="n">
         <v>50.99</v>
       </c>
-      <c r="F47" s="46" t="n">
+      <c r="F65" s="48" t="n">
         <v>54.22</v>
       </c>
-      <c r="G47" s="46" t="n">
+      <c r="G65" s="48" t="n">
         <v>57.85</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="27" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="27" t="inlineStr">
         <is>
           <t>WACC = 12.6%</t>
         </is>
       </c>
-      <c r="B48" s="25" t="n">
+      <c r="B66" s="25" t="n">
         <v>0.126</v>
       </c>
-      <c r="C48" s="46" t="n">
+      <c r="C66" s="48" t="n">
         <v>39.59</v>
       </c>
-      <c r="D48" s="46" t="n">
+      <c r="D66" s="48" t="n">
         <v>41.66</v>
       </c>
-      <c r="E48" s="46" t="n">
+      <c r="E66" s="48" t="n">
         <v>43.94</v>
       </c>
-      <c r="F48" s="46" t="n">
+      <c r="F66" s="48" t="n">
         <v>46.45</v>
       </c>
-      <c r="G48" s="46" t="n">
+      <c r="G66" s="48" t="n">
         <v>49.24</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="27" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="27" t="inlineStr">
         <is>
           <t>WACC = 13.6%</t>
         </is>
       </c>
-      <c r="B49" s="25" t="n">
+      <c r="B67" s="25" t="n">
         <v>0.136</v>
       </c>
-      <c r="C49" s="46" t="n">
+      <c r="C67" s="48" t="n">
         <v>34.75</v>
       </c>
-      <c r="D49" s="46" t="n">
+      <c r="D67" s="48" t="n">
         <v>36.43</v>
       </c>
-      <c r="E49" s="46" t="n">
+      <c r="E67" s="48" t="n">
         <v>38.25</v>
       </c>
-      <c r="F49" s="46" t="n">
+      <c r="F67" s="48" t="n">
         <v>40.25</v>
       </c>
-      <c r="G49" s="46" t="n">
+      <c r="G67" s="48" t="n">
         <v>42.45</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 6: SENSITIVITY — Share Price vs WACC &amp; EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="B70" s="17" t="n"/>
+      <c r="C70" s="17" t="n"/>
+      <c r="D70" s="17" t="n"/>
+      <c r="E70" s="17" t="n"/>
+      <c r="F70" s="17" t="n"/>
+      <c r="G70" s="17" t="n"/>
+      <c r="H70" s="17" t="n"/>
+      <c r="I70" s="17" t="n"/>
+      <c r="J70" s="17" t="n"/>
+      <c r="K70" s="17" t="n"/>
+      <c r="L70" s="17" t="n"/>
+      <c r="M70" s="17" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
+        <is>
+          <t>→ EV/EBITDA Exit Multiple</t>
+        </is>
+      </c>
+      <c r="C71" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="D71" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="E71" s="50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F71" s="50" t="n">
+        <v>23</v>
+      </c>
+      <c r="G71" s="50" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
+        <is>
+          <t>WACC = 9.6%</t>
+        </is>
+      </c>
+      <c r="B72" s="25" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="C72" s="48" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="D72" s="48" t="n">
+        <v>161.95</v>
+      </c>
+      <c r="E72" s="48" t="n">
+        <v>190.53</v>
+      </c>
+      <c r="F72" s="48" t="n">
+        <v>219.11</v>
+      </c>
+      <c r="G72" s="48" t="n">
+        <v>238.16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
+        <is>
+          <t>WACC = 10.6%</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="C73" s="48" t="n">
+        <v>136.55</v>
+      </c>
+      <c r="D73" s="48" t="n">
+        <v>154.76</v>
+      </c>
+      <c r="E73" s="48" t="n">
+        <v>182.07</v>
+      </c>
+      <c r="F73" s="48" t="n">
+        <v>209.38</v>
+      </c>
+      <c r="G73" s="48" t="n">
+        <v>227.59</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
+        <is>
+          <t>WACC = 11.6%</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="C74" s="48" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="D74" s="48" t="n">
+        <v>147.95</v>
+      </c>
+      <c r="E74" s="49" t="n">
+        <v>174.06</v>
+      </c>
+      <c r="F74" s="48" t="n">
+        <v>200.17</v>
+      </c>
+      <c r="G74" s="48" t="n">
+        <v>217.57</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="27" t="inlineStr">
+        <is>
+          <t>WACC = 12.6%</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="n">
+        <v>0.126</v>
+      </c>
+      <c r="C75" s="48" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="D75" s="48" t="n">
+        <v>141.49</v>
+      </c>
+      <c r="E75" s="48" t="n">
+        <v>166.46</v>
+      </c>
+      <c r="F75" s="48" t="n">
+        <v>191.43</v>
+      </c>
+      <c r="G75" s="48" t="n">
+        <v>208.08</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="27" t="inlineStr">
+        <is>
+          <t>WACC = 13.6%</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="C76" s="48" t="n">
+        <v>119.45</v>
+      </c>
+      <c r="D76" s="48" t="n">
+        <v>135.38</v>
+      </c>
+      <c r="E76" s="48" t="n">
+        <v>159.26</v>
+      </c>
+      <c r="F76" s="48" t="n">
+        <v>183.15</v>
+      </c>
+      <c r="G76" s="48" t="n">
+        <v>199.08</v>
       </c>
     </row>
   </sheetData>
@@ -4208,7 +4627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4278,10 +4697,10 @@
           <t>Market Cap / Equity Value ($M)</t>
         </is>
       </c>
-      <c r="B5" s="41" t="n">
-        <v>4249933.053952</v>
-      </c>
-      <c r="C5" s="48" t="inlineStr">
+      <c r="B5" s="42" t="n">
+        <v>4532958.920704</v>
+      </c>
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>Share price × diluted shares</t>
         </is>
@@ -4298,10 +4717,10 @@
           <t>Total Debt ($M)</t>
         </is>
       </c>
-      <c r="B6" s="41" t="n">
+      <c r="B6" s="42" t="n">
         <v>84710.998016</v>
       </c>
-      <c r="C6" s="48" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>ST + LT debt from Balance Sheet</t>
         </is>
@@ -4370,10 +4789,10 @@
           <t>Risk-Free Rate (Rf)</t>
         </is>
       </c>
-      <c r="B12" s="49" t="n">
+      <c r="B12" s="52" t="n">
         <v>0.045</v>
       </c>
-      <c r="C12" s="48" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
         <is>
           <t>10-year US Treasury yield</t>
         </is>
@@ -4385,10 +4804,10 @@
           <t>Equity Risk Premium (ERP)</t>
         </is>
       </c>
-      <c r="B13" s="49" t="n">
+      <c r="B13" s="52" t="n">
         <v>0.055</v>
       </c>
-      <c r="C13" s="48" t="inlineStr">
+      <c r="C13" s="51" t="inlineStr">
         <is>
           <t>Damodaran implied ERP</t>
         </is>
@@ -4397,15 +4816,15 @@
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
-          <t>Beta (Levered β)</t>
-        </is>
-      </c>
-      <c r="B14" s="50" t="n">
-        <v>1.086</v>
-      </c>
-      <c r="C14" s="48" t="inlineStr">
-        <is>
-          <t>Source: Yahoo Finance</t>
+          <t>Beta (Blume-Adjusted, Levered β)</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="n">
+        <v>1.1172</v>
+      </c>
+      <c r="C14" s="51" t="inlineStr">
+        <is>
+          <t>Blume adj: ⅔×1.1759 + ⅓×1.0 = 1.1172  |  Raw OLS derived: 1.1759</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4834,7 @@
           <t>Cost of Equity (Re)</t>
         </is>
       </c>
-      <c r="B15" s="51">
+      <c r="B15" s="54">
         <f>B12+B14*B13</f>
         <v/>
       </c>
@@ -4445,10 +4864,10 @@
           <t>Pre-Tax Cost of Debt (Rd)</t>
         </is>
       </c>
-      <c r="B18" s="49" t="n">
+      <c r="B18" s="52" t="n">
         <v>0.05</v>
       </c>
-      <c r="C18" s="48" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>Yield on outstanding bonds</t>
         </is>
@@ -4460,10 +4879,10 @@
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="B19" s="49" t="n">
+      <c r="B19" s="52" t="n">
         <v>0.21</v>
       </c>
-      <c r="C19" s="48" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>Effective tax rate — Source: Yahoo Finance</t>
         </is>
@@ -4527,7 +4946,7 @@
           <t>WACC = (E/V)×Re + (D/V)×Rd×(1-T)</t>
         </is>
       </c>
-      <c r="B25" s="51">
+      <c r="B25" s="54">
         <f>B23+B24</f>
         <v/>
       </c>
@@ -4537,8 +4956,418 @@
         </is>
       </c>
     </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>BETA DERIVATION — STEP-BY-STEP (OLS Regression, 5Y Weekly vs S&amp;P 500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>Formula / Source</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SETUP</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+      <c r="M29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>Regression Period</t>
+        </is>
+      </c>
+      <c r="B30" s="55" t="inlineStr">
+        <is>
+          <t>5 Years</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>5Y weekly (Fri-to-Fri) price returns</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>5Y window balances recency vs statistical robustness</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Benchmark</t>
+        </is>
+      </c>
+      <c r="B31" s="55" t="inlineStr">
+        <is>
+          <t>S&amp;P 500 (^GSPC)</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>Standard US equity market proxy</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Used as the market portfolio in CAPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Observations (N)</t>
+        </is>
+      </c>
+      <c r="B32" s="56" t="n">
+        <v>261</v>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>Weekly return pairs aligned on common trading dates</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 1 — RETURN STATISTICS</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n"/>
+      <c r="M34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>Avg weekly return — Stock</t>
+        </is>
+      </c>
+      <c r="B35" s="57" t="n">
+        <v>0.003847</v>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>Mean of 261 weekly returns</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="inlineStr">
+        <is>
+          <t>Simple arithmetic mean of weekly percentage returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>Avg weekly return — S&amp;P 500</t>
+        </is>
+      </c>
+      <c r="B36" s="57" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Mean of 261 weekly S&amp;P 500 returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Std dev — Stock weekly returns</t>
+        </is>
+      </c>
+      <c r="B37" s="57" t="n">
+        <v>0.03786</v>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>σ_stock = 3.7860%</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>Measures total volatility of the stock's weekly returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Std dev — S&amp;P 500 weekly returns</t>
+        </is>
+      </c>
+      <c r="B38" s="57" t="n">
+        <v>0.022476</v>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>σ_mkt = 2.2476%</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>Measures total volatility of the market's weekly returns</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 2 — COVARIANCE &amp; VARIANCE</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17" t="n"/>
+      <c r="L40" s="17" t="n"/>
+      <c r="M40" s="17" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>Cov(Stock, S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="B41" s="58" t="n">
+        <v>0.0005940299999999999</v>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>Cov = E[(r_stock − μ_stock)(r_mkt − μ_mkt)]</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>How much stock &amp; market returns move together; higher = more correlated</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>Var(S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="B42" s="58" t="n">
+        <v>0.00050518</v>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>Var = E[(r_mkt − μ_mkt)²]  =  σ_mkt²</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>Market's own return variance; normalises the covariance to give beta</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 3 — RAW BETA = Cov / Var</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="17" t="n"/>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="17" t="n"/>
+      <c r="J44" s="17" t="n"/>
+      <c r="K44" s="17" t="n"/>
+      <c r="L44" s="17" t="n"/>
+      <c r="M44" s="17" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="27" t="inlineStr">
+        <is>
+          <t>Raw Beta (OLS slope)</t>
+        </is>
+      </c>
+      <c r="B45" s="59" t="n">
+        <v>1.1759</v>
+      </c>
+      <c r="C45" s="32">
+        <f> 0.00059403 / 0.00050518</f>
+        <v/>
+      </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>OLS regression slope; how much the stock moves per 1% market move</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>R-Squared (R²)</t>
+        </is>
+      </c>
+      <c r="B46" s="60" t="n">
+        <v>0.4873</v>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>R² = Corr(r_stock, r_mkt)²</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>% of stock return variance explained by market; remainder is idiosyncratic risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 4 — BLUME ADJUSTMENT = ⅔ × Raw Beta + ⅓ × 1.0</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="17" t="n"/>
+      <c r="H48" s="17" t="n"/>
+      <c r="I48" s="17" t="n"/>
+      <c r="J48" s="17" t="n"/>
+      <c r="K48" s="17" t="n"/>
+      <c r="L48" s="17" t="n"/>
+      <c r="M48" s="17" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>⅔ × Raw Beta</t>
+        </is>
+      </c>
+      <c r="B49" s="60" t="n">
+        <v>0.7839</v>
+      </c>
+      <c r="C49" s="32">
+        <f> ⅔ × 1.1759 = 0.7839</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>⅓ × 1.0 (mean-reversion anchor)</t>
+        </is>
+      </c>
+      <c r="B50" s="60" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="C50" s="32">
+        <f> ⅓ × 1.0 = 0.3333</f>
+        <v/>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>Blume (1975): raw betas revert toward 1.0 over time</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>Adjusted Beta → used in CAPM above</t>
+        </is>
+      </c>
+      <c r="B51" s="61" t="n">
+        <v>1.1172</v>
+      </c>
+      <c r="C51" s="32">
+        <f> 0.7839 + 0.3333 = 1.1172</f>
+        <v/>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>This value is the Beta input in the CAPM section above</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="29" t="inlineStr">
+        <is>
+          <t>Yahoo Finance Beta (reference only)</t>
+        </is>
+      </c>
+      <c r="B52" s="62" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>YF uses 5Y monthly returns vs S&amp;P 500 — slightly different methodology</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Shown for comparison only; OLS-derived beta used in this model</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4647,44 +5476,44 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="52" t="inlineStr">
+      <c r="A4" s="63" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="B4" s="52" t="inlineStr">
+      <c r="B4" s="63" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C4" s="53" t="n">
-        <v>4249933.053952</v>
-      </c>
-      <c r="D4" s="53" t="n">
+      <c r="C4" s="64" t="n">
+        <v>4532958.920704</v>
+      </c>
+      <c r="D4" s="64" t="n">
         <v>84710.998016</v>
       </c>
-      <c r="E4" s="53" t="n">
+      <c r="E4" s="64" t="n">
         <v>-68507.00083200001</v>
       </c>
-      <c r="F4" s="53" t="n">
-        <v>4266137.051136</v>
-      </c>
-      <c r="G4" s="53" t="n">
+      <c r="F4" s="64" t="n">
+        <v>4549162.917888</v>
+      </c>
+      <c r="G4" s="64" t="n">
         <v>451442.016256</v>
       </c>
-      <c r="H4" s="53" t="n">
+      <c r="H4" s="64" t="n">
         <v>159975.99744</v>
       </c>
-      <c r="I4" s="54">
+      <c r="I4" s="65">
         <f>F4/G4</f>
         <v/>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="65">
         <f>F4/H4</f>
         <v/>
       </c>
-      <c r="K4" s="54" t="n">
-        <v>35.073936</v>
+      <c r="K4" s="65" t="n">
+        <v>37.319225</v>
       </c>
       <c r="M4" s="22" t="inlineStr">
         <is>
@@ -4703,22 +5532,22 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="C5" s="55" t="n">
-        <v>2770954.62</v>
-      </c>
-      <c r="D5" s="55" t="n">
+      <c r="C5" s="66" t="n">
+        <v>2900729.53</v>
+      </c>
+      <c r="D5" s="66" t="n">
         <v>125432</v>
       </c>
-      <c r="E5" s="55" t="n">
+      <c r="E5" s="66" t="n">
         <v>-78228</v>
       </c>
-      <c r="F5" s="55" t="n">
-        <v>2818158.62</v>
-      </c>
-      <c r="G5" s="55" t="n">
+      <c r="F5" s="66" t="n">
+        <v>2947933.53</v>
+      </c>
+      <c r="G5" s="66" t="n">
         <v>318273</v>
       </c>
-      <c r="H5" s="55" t="n">
+      <c r="H5" s="66" t="n">
         <v>184457</v>
       </c>
       <c r="I5" s="34">
@@ -4730,7 +5559,7 @@
         <v/>
       </c>
       <c r="K5" s="34" t="n">
-        <v>22.19</v>
+        <v>23.26</v>
       </c>
       <c r="M5" s="22" t="inlineStr">
         <is>
@@ -4749,22 +5578,22 @@
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="C6" s="55" t="n">
-        <v>4360833.34</v>
-      </c>
-      <c r="D6" s="55" t="n">
+      <c r="C6" s="66" t="n">
+        <v>4391827.93</v>
+      </c>
+      <c r="D6" s="66" t="n">
         <v>95876</v>
       </c>
-      <c r="E6" s="55" t="n">
+      <c r="E6" s="66" t="n">
         <v>-126840</v>
       </c>
-      <c r="F6" s="55" t="n">
-        <v>4329869.34</v>
-      </c>
-      <c r="G6" s="55" t="n">
+      <c r="F6" s="66" t="n">
+        <v>4360863.93</v>
+      </c>
+      <c r="G6" s="66" t="n">
         <v>422498.01</v>
       </c>
-      <c r="H6" s="55" t="n">
+      <c r="H6" s="66" t="n">
         <v>161316</v>
       </c>
       <c r="I6" s="34">
@@ -4776,7 +5605,7 @@
         <v/>
       </c>
       <c r="K6" s="34" t="n">
-        <v>27.24</v>
+        <v>27.47</v>
       </c>
       <c r="M6" s="22" t="inlineStr">
         <is>
@@ -4795,22 +5624,22 @@
           <t>META</t>
         </is>
       </c>
-      <c r="C7" s="55" t="n">
-        <v>1429868.38</v>
-      </c>
-      <c r="D7" s="55" t="n">
+      <c r="C7" s="66" t="n">
+        <v>1479647.04</v>
+      </c>
+      <c r="D7" s="66" t="n">
         <v>86769</v>
       </c>
-      <c r="E7" s="55" t="n">
+      <c r="E7" s="66" t="n">
         <v>-81180</v>
       </c>
-      <c r="F7" s="55" t="n">
-        <v>1435457.38</v>
-      </c>
-      <c r="G7" s="55" t="n">
+      <c r="F7" s="66" t="n">
+        <v>1485236.04</v>
+      </c>
+      <c r="G7" s="66" t="n">
         <v>214963</v>
       </c>
-      <c r="H7" s="55" t="n">
+      <c r="H7" s="66" t="n">
         <v>109308</v>
       </c>
       <c r="I7" s="34">
@@ -4822,7 +5651,7 @@
         <v/>
       </c>
       <c r="K7" s="34" t="n">
-        <v>20.49</v>
+        <v>21.18</v>
       </c>
       <c r="M7" s="22" t="inlineStr">
         <is>
@@ -4841,22 +5670,22 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="C8" s="55" t="n">
-        <v>2563849.58</v>
-      </c>
-      <c r="D8" s="55" t="n">
+      <c r="C8" s="66" t="n">
+        <v>2610427.85</v>
+      </c>
+      <c r="D8" s="66" t="n">
         <v>235540</v>
       </c>
-      <c r="E8" s="55" t="n">
+      <c r="E8" s="66" t="n">
         <v>-143088.99</v>
       </c>
-      <c r="F8" s="55" t="n">
-        <v>2656300.6</v>
-      </c>
-      <c r="G8" s="55" t="n">
+      <c r="F8" s="66" t="n">
+        <v>2702878.87</v>
+      </c>
+      <c r="G8" s="66" t="n">
         <v>742775.98</v>
       </c>
-      <c r="H8" s="55" t="n">
+      <c r="H8" s="66" t="n">
         <v>155860.99</v>
       </c>
       <c r="I8" s="34">
@@ -4868,7 +5697,7 @@
         <v/>
       </c>
       <c r="K8" s="34" t="n">
-        <v>31.65</v>
+        <v>31.76</v>
       </c>
       <c r="M8" s="22" t="inlineStr">
         <is>
@@ -4887,22 +5716,22 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="C9" s="55" t="n">
-        <v>4846379.86</v>
-      </c>
-      <c r="D9" s="55" t="n">
+      <c r="C9" s="66" t="n">
+        <v>4718977.35</v>
+      </c>
+      <c r="D9" s="66" t="n">
         <v>12814</v>
       </c>
-      <c r="E9" s="55" t="n">
+      <c r="E9" s="66" t="n">
         <v>-53172</v>
       </c>
-      <c r="F9" s="55" t="n">
-        <v>4806021.86</v>
-      </c>
-      <c r="G9" s="55" t="n">
+      <c r="F9" s="66" t="n">
+        <v>4678619.35</v>
+      </c>
+      <c r="G9" s="66" t="n">
         <v>253491</v>
       </c>
-      <c r="H9" s="55" t="n">
+      <c r="H9" s="66" t="n">
         <v>165514</v>
       </c>
       <c r="I9" s="34">
@@ -4914,7 +5743,7 @@
         <v/>
       </c>
       <c r="K9" s="34" t="n">
-        <v>30.64</v>
+        <v>29.88</v>
       </c>
       <c r="M9" s="22" t="inlineStr">
         <is>
@@ -4923,39 +5752,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="56" t="inlineStr">
+      <c r="A11" s="67" t="inlineStr">
         <is>
           <t>Peer Mean</t>
         </is>
       </c>
-      <c r="I11" s="57">
+      <c r="I11" s="59">
         <f>AVERAGE(I5:I9)</f>
         <v/>
       </c>
-      <c r="J11" s="57">
+      <c r="J11" s="59">
         <f>AVERAGE(J5:J9)</f>
         <v/>
       </c>
-      <c r="K11" s="57">
+      <c r="K11" s="59">
         <f>AVERAGE(K5:K9)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="56" t="inlineStr">
+      <c r="A12" s="67" t="inlineStr">
         <is>
           <t>Peer Median</t>
         </is>
       </c>
-      <c r="I12" s="57">
+      <c r="I12" s="59">
         <f>MEDIAN(I5:I9)</f>
         <v/>
       </c>
-      <c r="J12" s="57">
+      <c r="J12" s="59">
         <f>MEDIAN(J5:J9)</f>
         <v/>
       </c>
-      <c r="K12" s="57">
+      <c r="K12" s="59">
         <f>MEDIAN(K5:K9)</f>
         <v/>
       </c>
@@ -4995,7 +5824,7 @@
           <t>Diluted Shares (M)</t>
         </is>
       </c>
-      <c r="B17" s="58" t="n">
+      <c r="B17" s="60" t="n">
         <v>14687.356</v>
       </c>
     </row>
@@ -5005,7 +5834,7 @@
           <t>Implied Share Price (Comps-based)</t>
         </is>
       </c>
-      <c r="B18" s="44">
+      <c r="B18" s="46">
         <f>B16/B17</f>
         <v/>
       </c>
@@ -5096,13 +5925,13 @@
           <t>52-Week Trading Range</t>
         </is>
       </c>
-      <c r="B4" s="59" t="n">
+      <c r="B4" s="68" t="n">
         <v>201.5</v>
       </c>
-      <c r="C4" s="44" t="n">
-        <v>289.36</v>
-      </c>
-      <c r="D4" s="59" t="n">
+      <c r="C4" s="46" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="D4" s="68" t="n">
         <v>317.4</v>
       </c>
       <c r="E4" s="32" t="inlineStr">
@@ -5110,7 +5939,7 @@
           <t>Share price</t>
         </is>
       </c>
-      <c r="F4" s="60" t="n">
+      <c r="F4" s="69" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="22" t="inlineStr">
@@ -5125,21 +5954,21 @@
           <t>DCF — Base Case</t>
         </is>
       </c>
-      <c r="B5" s="59" t="n">
-        <v>245.956</v>
-      </c>
-      <c r="C5" s="44" t="n">
-        <v>300.9344</v>
-      </c>
-      <c r="D5" s="59" t="n">
-        <v>361.7</v>
+      <c r="B5" s="68" t="n">
+        <v>262.3355</v>
+      </c>
+      <c r="C5" s="46" t="n">
+        <v>320.9752</v>
+      </c>
+      <c r="D5" s="68" t="n">
+        <v>385.7875</v>
       </c>
       <c r="E5" s="32" t="inlineStr">
         <is>
           <t>UFCF + TV</t>
         </is>
       </c>
-      <c r="F5" s="60" t="n">
+      <c r="F5" s="69" t="n">
         <v>0.35</v>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -5154,21 +5983,21 @@
           <t>Trading Comps — EV/EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="59" t="n">
-        <v>260.424</v>
-      </c>
-      <c r="C6" s="44" t="n">
-        <v>289.36</v>
-      </c>
-      <c r="D6" s="59" t="n">
-        <v>332.764</v>
+      <c r="B6" s="68" t="n">
+        <v>277.767</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="D6" s="68" t="n">
+        <v>354.9245</v>
       </c>
       <c r="E6" s="32" t="inlineStr">
         <is>
           <t>LTM EBITDA</t>
         </is>
       </c>
-      <c r="F6" s="60" t="n">
+      <c r="F6" s="69" t="n">
         <v>0.25</v>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -5183,21 +6012,21 @@
           <t>Trading Comps — P/E</t>
         </is>
       </c>
-      <c r="B7" s="59" t="n">
-        <v>266.2112</v>
-      </c>
-      <c r="C7" s="44" t="n">
-        <v>300.9344</v>
-      </c>
-      <c r="D7" s="59" t="n">
-        <v>341.4448</v>
+      <c r="B7" s="68" t="n">
+        <v>283.9396</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>320.9752</v>
+      </c>
+      <c r="D7" s="68" t="n">
+        <v>364.1833999999999</v>
       </c>
       <c r="E7" s="32" t="inlineStr">
         <is>
           <t>LTM EPS</t>
         </is>
       </c>
-      <c r="F7" s="60" t="n">
+      <c r="F7" s="69" t="n">
         <v>0.25</v>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -5212,21 +6041,21 @@
           <t>Precedent Transactions</t>
         </is>
       </c>
-      <c r="B8" s="59" t="n">
-        <v>303.828</v>
-      </c>
-      <c r="C8" s="44" t="n">
-        <v>347.232</v>
-      </c>
-      <c r="D8" s="59" t="n">
-        <v>405.104</v>
+      <c r="B8" s="68" t="n">
+        <v>324.0615</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>370.356</v>
+      </c>
+      <c r="D8" s="68" t="n">
+        <v>432.082</v>
       </c>
       <c r="E8" s="32" t="inlineStr">
         <is>
           <t>LTM EBITDA</t>
         </is>
       </c>
-      <c r="F8" s="60" t="n">
+      <c r="F8" s="69" t="n">
         <v>0.15</v>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -5241,13 +6070,13 @@
           <t>Analyst Price Targets</t>
         </is>
       </c>
-      <c r="B9" s="59" t="n">
+      <c r="B9" s="68" t="n">
         <v>215</v>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="46" t="n">
         <v>315.09048</v>
       </c>
-      <c r="D9" s="59" t="n">
+      <c r="D9" s="68" t="n">
         <v>400</v>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -5255,7 +6084,7 @@
           <t>Consensus</t>
         </is>
       </c>
-      <c r="F9" s="60" t="n">
+      <c r="F9" s="69" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -5270,7 +6099,7 @@
           <t>Weighted Average Implied Price</t>
         </is>
       </c>
-      <c r="C11" s="61">
+      <c r="C11" s="70">
         <f>SUMPRODUCT(C4:C9,F4:F9)</f>
         <v/>
       </c>
@@ -5286,8 +6115,8 @@
           <t>Actual Market Price</t>
         </is>
       </c>
-      <c r="C12" s="61" t="n">
-        <v>289.36</v>
+      <c r="C12" s="70" t="n">
+        <v>308.63</v>
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
@@ -5330,17 +6159,17 @@
           <t>DCF</t>
         </is>
       </c>
-      <c r="B16" s="48" t="inlineStr">
+      <c r="B16" s="51" t="inlineStr">
         <is>
           <t>Intrinsic; captures unique characteristics</t>
         </is>
       </c>
-      <c r="C16" s="48" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>Sensitive to WACC &amp; g; needs detailed forecasts</t>
         </is>
       </c>
-      <c r="D16" s="48" t="inlineStr">
+      <c r="D16" s="51" t="inlineStr">
         <is>
           <t>Standalone; stable FCF companies</t>
         </is>
@@ -5352,17 +6181,17 @@
           <t>Trading Comps</t>
         </is>
       </c>
-      <c r="B17" s="48" t="inlineStr">
+      <c r="B17" s="51" t="inlineStr">
         <is>
           <t>Live market sentiment; easy to update</t>
         </is>
       </c>
-      <c r="C17" s="48" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>Market can misprice; peers may differ</t>
         </is>
       </c>
-      <c r="D17" s="48" t="inlineStr">
+      <c r="D17" s="51" t="inlineStr">
         <is>
           <t>Quick benchmarking; IPO pricing</t>
         </is>
@@ -5374,17 +6203,17 @@
           <t>Precedent Transactions</t>
         </is>
       </c>
-      <c r="B18" s="48" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>Includes control premium; real deal economics</t>
         </is>
       </c>
-      <c r="C18" s="48" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>Historical; market conditions change</t>
         </is>
       </c>
-      <c r="D18" s="48" t="inlineStr">
+      <c r="D18" s="51" t="inlineStr">
         <is>
           <t>M&amp;A advisory; fairness opinions</t>
         </is>
@@ -5396,17 +6225,17 @@
           <t>LBO Analysis</t>
         </is>
       </c>
-      <c r="B19" s="48" t="inlineStr">
+      <c r="B19" s="51" t="inlineStr">
         <is>
           <t>Sets floor for PE buyers; leverage capacity</t>
         </is>
       </c>
-      <c r="C19" s="48" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>Irrelevant for strategic buyers</t>
         </is>
       </c>
-      <c r="D19" s="48" t="inlineStr">
+      <c r="D19" s="51" t="inlineStr">
         <is>
           <t>Sponsored / PE deals</t>
         </is>
@@ -5418,17 +6247,17 @@
           <t>Sum-of-Parts (SOTP)</t>
         </is>
       </c>
-      <c r="B20" s="48" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>Values conglomerates properly by segment</t>
         </is>
       </c>
-      <c r="C20" s="48" t="inlineStr">
+      <c r="C20" s="51" t="inlineStr">
         <is>
           <t>Complex; needs separate comps per segment</t>
         </is>
       </c>
-      <c r="D20" s="48" t="inlineStr">
+      <c r="D20" s="51" t="inlineStr">
         <is>
           <t>Conglomerates; multi-segment cos</t>
         </is>
